--- a/Collaudo/Inventario_di_prova.xlsx
+++ b/Collaudo/Inventario_di_prova.xlsx
@@ -435,15 +435,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,20 +460,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Asset Function</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Modello/Descrizione</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Numero di serie</t>
         </is>
@@ -496,18 +502,23 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Lenovo ThinkPad T14 Gen 5</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>PF5BA01</t>
         </is>
@@ -526,20 +537,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Postazione 1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Lenovo ThinkPad T14 Gen 4</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>PF4BA02</t>
         </is>
@@ -556,18 +572,23 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PC Refresh</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Lenovo ThinkPad T14 Gen 5</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>PF5BA03</t>
         </is>
@@ -586,20 +607,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>Batteria da sostituire</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>In attesa ritiro</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Lenovo ThinkPad T14 Gen 4</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>PF4BA04</t>
         </is>
@@ -616,18 +642,23 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Guasto in attesa tecnico</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Lenovo ThinkPad T14 Gen 5</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>PF5BA05</t>
         </is>
@@ -646,20 +677,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>PC Refresh</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>Con custodia</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Da rebuildare</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Lenovo ThinkPad T14 Gen 4</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>PF4BA06</t>
         </is>
@@ -676,18 +712,23 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Controllare</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Lenovo ThinkPad T14 Gen 5</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>PF5BA07</t>
         </is>
@@ -706,20 +747,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>In verifica</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Dell Latitude 7320 Detachable</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>7HB108</t>
         </is>
@@ -736,18 +782,23 @@
           <t>Tablet</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Dell Latitude 7230 Rugged Extreme</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>8HB109</t>
         </is>
@@ -764,22 +815,23 @@
           <t>Tablet</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Scorta</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>Dell Latitude 7320 Detachable</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>4HB110</t>
         </is>
@@ -803,18 +855,23 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Lenovo ThinkPad T14 Gen 5</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>PF5KS01</t>
         </is>
@@ -833,20 +890,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Postazione 1</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>Lenovo ThinkPad T14 Gen 4</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>PF4KS02</t>
         </is>
@@ -863,18 +925,23 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PC Refresh</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Lenovo ThinkPad T14 Gen 5</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>PF5KS03</t>
         </is>
@@ -893,20 +960,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>Batteria da sostituire</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>In attesa ritiro</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Lenovo ThinkPad T14 Gen 4</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>PF4KS04</t>
         </is>
@@ -923,18 +995,23 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>Guasto in attesa tecnico</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Lenovo ThinkPad T14 Gen 5</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>PF5KS05</t>
         </is>
@@ -953,20 +1030,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>PC Refresh</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>Con custodia</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Da rebuildare</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Lenovo ThinkPad T14 Gen 4</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>PF4KS06</t>
         </is>
@@ -983,18 +1065,23 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
         <is>
           <t>Controllare</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Lenovo ThinkPad T14 Gen 5</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>PF5KS07</t>
         </is>
@@ -1013,20 +1100,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>In verifica</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Dell Latitude 7320 Detachable</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>7HK208</t>
         </is>
@@ -1043,18 +1135,23 @@
           <t>Tablet</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Dell Latitude 7230 Rugged Extreme</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>8HK209</t>
         </is>
@@ -1071,22 +1168,23 @@
           <t>Tablet</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Scorta</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>Dell Latitude 7320 Detachable</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>4HK210</t>
         </is>
@@ -1110,18 +1208,23 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>Lenovo ThinkPad T14 Gen 5</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>PF5DR01</t>
         </is>
@@ -1140,20 +1243,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>Postazione 1</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>Lenovo ThinkPad T14 Gen 4</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>PF4DR02</t>
         </is>
@@ -1170,18 +1278,23 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PC Refresh</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>Lenovo ThinkPad T14 Gen 5</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>PF5DR03</t>
         </is>
@@ -1200,20 +1313,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>Batteria da sostituire</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>In attesa ritiro</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Lenovo ThinkPad T14 Gen 4</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>PF4DR04</t>
         </is>
@@ -1230,18 +1348,23 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
         <is>
           <t>Guasto in attesa tecnico</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Lenovo ThinkPad T14 Gen 5</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>PF5DR05</t>
         </is>
@@ -1260,20 +1383,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>PC Refresh</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>Con custodia</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Da rebuildare</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Lenovo ThinkPad T14 Gen 4</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>PF4DR06</t>
         </is>
@@ -1290,18 +1418,23 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
         <is>
           <t>Controllare</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Lenovo ThinkPad T14 Gen 5</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>PF5DR07</t>
         </is>
@@ -1320,20 +1453,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>In verifica</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>Dell Latitude 7320 Detachable</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>7HD308</t>
         </is>
@@ -1350,18 +1488,23 @@
           <t>Tablet</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>Dell Latitude 7230 Rugged Extreme</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>8HD309</t>
         </is>
@@ -1378,22 +1521,23 @@
           <t>Tablet</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Scorta</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>Dell Latitude 7320 Detachable</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>4HD310</t>
         </is>
@@ -1401,9 +1545,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
